--- a/batch_04/Lookup_Conditionals.xlsx
+++ b/batch_04/Lookup_Conditionals.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="lookup" sheetId="4" r:id="rId1"/>
     <sheet name="LOGICAL FUNCTION" sheetId="5" r:id="rId2"/>
     <sheet name="Product" sheetId="1" r:id="rId3"/>
-    <sheet name="Sales" sheetId="2" r:id="rId4"/>
+    <sheet name="H&amp;V_Lookup" sheetId="6" r:id="rId4"/>
+    <sheet name="Sales" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="48">
   <si>
     <t>Product ID</t>
   </si>
@@ -162,6 +163,15 @@
   </si>
   <si>
     <t>Search by productid (v- mode)</t>
+  </si>
+  <si>
+    <t>Search by product id</t>
+  </si>
+  <si>
+    <t>Hlookup</t>
+  </si>
+  <si>
+    <t>Vlookup</t>
   </si>
 </sst>
 </file>
@@ -205,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +244,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1302,6 +1315,421 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:Q30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <f>VLOOKUP(A5,A9:D18,4,FALSE)</f>
+        <v>2400</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5">
+        <f>VLOOKUP(G5,B9:D18,3,FALSE)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="8">
+        <v>8000</v>
+      </c>
+      <c r="Q15">
+        <f>MATCH("Price",A28:A30,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="8">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <f>HLOOKUP(A23,B27:K30,4,FALSE)</f>
+        <v>700</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <f>HLOOKUP(G23,B28:K30,MATCH(K22,A28:A30,0),FALSE)</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="8">
+        <v>55000</v>
+      </c>
+      <c r="C30" s="8">
+        <v>700</v>
+      </c>
+      <c r="D30" s="8">
+        <v>1200</v>
+      </c>
+      <c r="E30" s="8">
+        <v>9000</v>
+      </c>
+      <c r="F30" s="8">
+        <v>15000</v>
+      </c>
+      <c r="G30" s="8">
+        <v>4500</v>
+      </c>
+      <c r="H30" s="8">
+        <v>8000</v>
+      </c>
+      <c r="I30" s="8">
+        <v>650</v>
+      </c>
+      <c r="J30" s="8">
+        <v>2400</v>
+      </c>
+      <c r="K30" s="8">
+        <v>1800</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
